--- a/sams-demand.xlsx
+++ b/sams-demand.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19150" windowHeight="6950"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8280"/>
   </bookViews>
   <sheets>
     <sheet name="需求计划" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="88">
   <si>
     <t>品牌 Code</t>
   </si>
@@ -181,6 +181,15 @@
   </si>
   <si>
     <t>2026-10 W2 (1005~1011)</t>
+  </si>
+  <si>
+    <t>2026-10 W3 (1012~1018)</t>
+  </si>
+  <si>
+    <t>2026-10 W4 (1019~1025)</t>
+  </si>
+  <si>
+    <t>2026-10 W5P1 (1026~1031)</t>
   </si>
   <si>
     <t>69</t>
@@ -602,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BB13"/>
+  <dimension ref="A1:BE13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="16" customWidth="1"/>
@@ -630,10 +639,11 @@
     <col min="47" max="48" width="40" customWidth="1"/>
     <col min="49" max="51" width="36" customWidth="1"/>
     <col min="52" max="53" width="40" customWidth="1"/>
-    <col min="54" max="54" width="36" customWidth="1"/>
+    <col min="54" max="56" width="36" customWidth="1"/>
+    <col min="57" max="57" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:57" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -796,70 +806,79 @@
       <c r="BB1" t="s">
         <v>53</v>
       </c>
+      <c r="BC1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="2" spans="1:54" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:57" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Q2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="S2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="T2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="W2">
         <v>6786</v>
@@ -942,70 +961,73 @@
       <c r="AZ2">
         <v>11310</v>
       </c>
+      <c r="BC2">
+        <v>10092</v>
+      </c>
     </row>
-    <row r="3" spans="1:54" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:57" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Q3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="S3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="T3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AV3">
         <v>5568</v>
@@ -1022,70 +1044,79 @@
       <c r="AZ3">
         <v>0</v>
       </c>
+      <c r="BC3">
+        <v>13731</v>
+      </c>
+      <c r="BD3">
+        <v>15450</v>
+      </c>
+      <c r="BE3">
+        <v>15956</v>
+      </c>
     </row>
-    <row r="4" spans="1:54" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:57" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M4" t="s">
+        <v>69</v>
+      </c>
+      <c r="N4" t="s">
+        <v>70</v>
+      </c>
+      <c r="O4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>72</v>
+      </c>
+      <c r="R4" t="s">
+        <v>73</v>
+      </c>
+      <c r="S4" t="s">
+        <v>74</v>
+      </c>
+      <c r="T4" t="s">
         <v>75</v>
       </c>
-      <c r="H4" t="s">
+      <c r="U4" t="s">
         <v>76</v>
-      </c>
-      <c r="I4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J4" t="s">
-        <v>63</v>
-      </c>
-      <c r="K4" t="s">
-        <v>64</v>
-      </c>
-      <c r="L4" t="s">
-        <v>65</v>
-      </c>
-      <c r="M4" t="s">
-        <v>66</v>
-      </c>
-      <c r="N4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O4" t="s">
-        <v>54</v>
-      </c>
-      <c r="P4" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>69</v>
-      </c>
-      <c r="R4" t="s">
-        <v>70</v>
-      </c>
-      <c r="S4" t="s">
-        <v>71</v>
-      </c>
-      <c r="T4" t="s">
-        <v>72</v>
-      </c>
-      <c r="U4" t="s">
-        <v>73</v>
       </c>
       <c r="V4">
         <v>1392</v>
@@ -1177,70 +1208,73 @@
       <c r="BB4">
         <v>10962</v>
       </c>
+      <c r="BC4">
+        <v>14268</v>
+      </c>
     </row>
-    <row r="5" spans="1:54" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:57" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" t="s">
+        <v>69</v>
+      </c>
+      <c r="N5" t="s">
+        <v>70</v>
+      </c>
+      <c r="O5" t="s">
+        <v>57</v>
+      </c>
+      <c r="P5" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>72</v>
+      </c>
+      <c r="R5" t="s">
+        <v>73</v>
+      </c>
+      <c r="S5" t="s">
+        <v>74</v>
+      </c>
+      <c r="T5" t="s">
         <v>75</v>
       </c>
-      <c r="H5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5" t="s">
-        <v>63</v>
-      </c>
-      <c r="K5" t="s">
-        <v>64</v>
-      </c>
-      <c r="L5" t="s">
-        <v>65</v>
-      </c>
-      <c r="M5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N5" t="s">
-        <v>67</v>
-      </c>
-      <c r="O5" t="s">
-        <v>54</v>
-      </c>
-      <c r="P5" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>69</v>
-      </c>
-      <c r="R5" t="s">
-        <v>70</v>
-      </c>
-      <c r="S5" t="s">
-        <v>71</v>
-      </c>
-      <c r="T5" t="s">
-        <v>72</v>
-      </c>
       <c r="U5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AV5">
         <v>10092</v>
@@ -1260,70 +1294,79 @@
       <c r="BB5">
         <v>10962</v>
       </c>
+      <c r="BC5">
+        <v>16380</v>
+      </c>
+      <c r="BD5">
+        <v>18430</v>
+      </c>
+      <c r="BE5">
+        <v>19030</v>
+      </c>
     </row>
-    <row r="6" spans="1:54" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:57" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Q6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="S6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="T6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AF6">
         <v>3132</v>
@@ -1385,147 +1428,159 @@
       <c r="BB6">
         <v>1566</v>
       </c>
+      <c r="BC6">
+        <v>5742</v>
+      </c>
     </row>
-    <row r="7" spans="1:54" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:57" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K7" t="s">
+        <v>67</v>
+      </c>
+      <c r="L7" t="s">
+        <v>68</v>
+      </c>
+      <c r="M7" t="s">
+        <v>69</v>
+      </c>
+      <c r="N7" t="s">
+        <v>70</v>
+      </c>
+      <c r="O7" t="s">
+        <v>57</v>
+      </c>
+      <c r="P7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R7" t="s">
+        <v>73</v>
+      </c>
+      <c r="S7" t="s">
+        <v>74</v>
+      </c>
+      <c r="T7" t="s">
+        <v>75</v>
+      </c>
+      <c r="U7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
         <v>58</v>
       </c>
-      <c r="F7" t="s">
+      <c r="C8" t="s">
         <v>59</v>
       </c>
-      <c r="G7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="D8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" t="s">
         <v>62</v>
       </c>
-      <c r="J7" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="G8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" t="s">
         <v>65</v>
       </c>
-      <c r="M7" t="s">
+      <c r="J8" t="s">
         <v>66</v>
       </c>
-      <c r="N7" t="s">
+      <c r="K8" t="s">
         <v>67</v>
       </c>
-      <c r="O7" t="s">
-        <v>54</v>
-      </c>
-      <c r="P7" t="s">
+      <c r="L8" t="s">
         <v>68</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="M8" t="s">
         <v>69</v>
       </c>
-      <c r="R7" t="s">
+      <c r="N8" t="s">
         <v>70</v>
       </c>
-      <c r="S7" t="s">
+      <c r="O8" t="s">
+        <v>57</v>
+      </c>
+      <c r="P8" t="s">
         <v>71</v>
       </c>
-      <c r="T7" t="s">
+      <c r="Q8" t="s">
         <v>72</v>
       </c>
-      <c r="U7" t="s">
+      <c r="R8" t="s">
+        <v>73</v>
+      </c>
+      <c r="S8" t="s">
         <v>74</v>
       </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:54" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" t="s">
-        <v>79</v>
-      </c>
-      <c r="H8" t="s">
-        <v>80</v>
-      </c>
-      <c r="I8" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" t="s">
-        <v>63</v>
-      </c>
-      <c r="K8" t="s">
-        <v>64</v>
-      </c>
-      <c r="L8" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8" t="s">
-        <v>66</v>
-      </c>
-      <c r="N8" t="s">
-        <v>67</v>
-      </c>
-      <c r="O8" t="s">
-        <v>54</v>
-      </c>
-      <c r="P8" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>69</v>
-      </c>
-      <c r="R8" t="s">
-        <v>70</v>
-      </c>
-      <c r="S8" t="s">
-        <v>71</v>
-      </c>
       <c r="T8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AF8">
         <v>2610</v>
@@ -1587,147 +1642,159 @@
       <c r="BB8">
         <v>1392</v>
       </c>
+      <c r="BC8">
+        <v>3480</v>
+      </c>
     </row>
-    <row r="9" spans="1:54" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:57" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" t="s">
+        <v>66</v>
+      </c>
+      <c r="K9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L9" t="s">
+        <v>68</v>
+      </c>
+      <c r="M9" t="s">
+        <v>69</v>
+      </c>
+      <c r="N9" t="s">
+        <v>70</v>
+      </c>
+      <c r="O9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P9" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>72</v>
+      </c>
+      <c r="R9" t="s">
+        <v>73</v>
+      </c>
+      <c r="S9" t="s">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s">
+        <v>75</v>
+      </c>
+      <c r="U9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:57" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
         <v>58</v>
       </c>
-      <c r="F9" t="s">
+      <c r="C10" t="s">
         <v>59</v>
       </c>
-      <c r="G9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="D10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s">
         <v>62</v>
       </c>
-      <c r="J9" t="s">
-        <v>63</v>
-      </c>
-      <c r="K9" t="s">
-        <v>64</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="G10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" t="s">
         <v>65</v>
       </c>
-      <c r="M9" t="s">
+      <c r="J10" t="s">
         <v>66</v>
       </c>
-      <c r="N9" t="s">
+      <c r="K10" t="s">
         <v>67</v>
       </c>
-      <c r="O9" t="s">
-        <v>54</v>
-      </c>
-      <c r="P9" t="s">
+      <c r="L10" t="s">
         <v>68</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="M10" t="s">
         <v>69</v>
       </c>
-      <c r="R9" t="s">
+      <c r="N10" t="s">
         <v>70</v>
       </c>
-      <c r="S9" t="s">
+      <c r="O10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P10" t="s">
         <v>71</v>
       </c>
-      <c r="T9" t="s">
+      <c r="Q10" t="s">
         <v>72</v>
       </c>
-      <c r="U9" t="s">
+      <c r="R10" t="s">
+        <v>73</v>
+      </c>
+      <c r="S10" t="s">
         <v>74</v>
       </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:54" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K10" t="s">
-        <v>64</v>
-      </c>
-      <c r="L10" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" t="s">
-        <v>66</v>
-      </c>
-      <c r="N10" t="s">
-        <v>67</v>
-      </c>
-      <c r="O10" t="s">
-        <v>54</v>
-      </c>
-      <c r="P10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R10" t="s">
-        <v>70</v>
-      </c>
-      <c r="S10" t="s">
-        <v>71</v>
-      </c>
       <c r="T10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AF10">
         <v>4002</v>
@@ -1789,147 +1856,159 @@
       <c r="BB10">
         <v>2436</v>
       </c>
+      <c r="BC10">
+        <v>3132</v>
+      </c>
     </row>
-    <row r="11" spans="1:54" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:57" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" t="s">
+        <v>68</v>
+      </c>
+      <c r="M11" t="s">
+        <v>69</v>
+      </c>
+      <c r="N11" t="s">
+        <v>70</v>
+      </c>
+      <c r="O11" t="s">
+        <v>57</v>
+      </c>
+      <c r="P11" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>72</v>
+      </c>
+      <c r="R11" t="s">
+        <v>73</v>
+      </c>
+      <c r="S11" t="s">
+        <v>74</v>
+      </c>
+      <c r="T11" t="s">
+        <v>75</v>
+      </c>
+      <c r="U11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:57" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
         <v>58</v>
       </c>
-      <c r="F11" t="s">
+      <c r="C12" t="s">
         <v>59</v>
       </c>
-      <c r="G11" t="s">
-        <v>81</v>
-      </c>
-      <c r="H11" t="s">
-        <v>82</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" t="s">
         <v>62</v>
       </c>
-      <c r="J11" t="s">
-        <v>63</v>
-      </c>
-      <c r="K11" t="s">
-        <v>64</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="G12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" t="s">
         <v>65</v>
       </c>
-      <c r="M11" t="s">
+      <c r="J12" t="s">
         <v>66</v>
       </c>
-      <c r="N11" t="s">
+      <c r="K12" t="s">
         <v>67</v>
       </c>
-      <c r="O11" t="s">
-        <v>54</v>
-      </c>
-      <c r="P11" t="s">
+      <c r="L12" t="s">
         <v>68</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="M12" t="s">
         <v>69</v>
       </c>
-      <c r="R11" t="s">
+      <c r="N12" t="s">
         <v>70</v>
       </c>
-      <c r="S11" t="s">
+      <c r="O12" t="s">
+        <v>57</v>
+      </c>
+      <c r="P12" t="s">
         <v>71</v>
       </c>
-      <c r="T11" t="s">
+      <c r="Q12" t="s">
         <v>72</v>
       </c>
-      <c r="U11" t="s">
+      <c r="R12" t="s">
+        <v>73</v>
+      </c>
+      <c r="S12" t="s">
         <v>74</v>
       </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:54" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" t="s">
-        <v>62</v>
-      </c>
-      <c r="J12" t="s">
-        <v>63</v>
-      </c>
-      <c r="K12" t="s">
-        <v>64</v>
-      </c>
-      <c r="L12" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12" t="s">
-        <v>66</v>
-      </c>
-      <c r="N12" t="s">
-        <v>67</v>
-      </c>
-      <c r="O12" t="s">
-        <v>54</v>
-      </c>
-      <c r="P12" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>69</v>
-      </c>
-      <c r="R12" t="s">
-        <v>70</v>
-      </c>
-      <c r="S12" t="s">
-        <v>71</v>
-      </c>
       <c r="T12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AF12">
         <v>5220</v>
@@ -1994,70 +2073,73 @@
       <c r="BB12">
         <v>4176</v>
       </c>
+      <c r="BC12">
+        <v>9918</v>
+      </c>
     </row>
-    <row r="13" spans="1:54" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:57" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L13" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Q13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="S13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="T13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AW13">
         <v>0</v>
@@ -2069,11 +2151,21 @@
         <v>0</v>
       </c>
       <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/sams-demand.xlsx
+++ b/sams-demand.xlsx
@@ -742,6 +742,9 @@
       <c r="BD2">
         <v>10440</v>
       </c>
+      <c r="BE2">
+        <v>2436</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1010,6 +1013,9 @@
       <c r="BD4">
         <v>12354</v>
       </c>
+      <c r="BE4">
+        <v>5394</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1471,6 +1477,9 @@
       <c r="BD8">
         <v>2262</v>
       </c>
+      <c r="BE8">
+        <v>1218</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1691,6 +1700,9 @@
       <c r="BD10">
         <v>6612</v>
       </c>
+      <c r="BE10">
+        <v>1914</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1913,6 +1925,9 @@
       </c>
       <c r="BD12">
         <v>11832</v>
+      </c>
+      <c r="BE12">
+        <v>2784</v>
       </c>
     </row>
     <row r="13">

--- a/sams-demand.xlsx
+++ b/sams-demand.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BK13"/>
+  <dimension ref="A1:BH13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -581,15 +581,6 @@
       <c r="BH1" t="str">
         <v>2026-11 W3 (1109~1115)</v>
       </c>
-      <c r="BI1" t="str">
-        <v>2026-11 W4 (1116~1122)</v>
-      </c>
-      <c r="BJ1" t="str">
-        <v>2026-11 W5 (1123~1129)</v>
-      </c>
-      <c r="BK1" t="str">
-        <v>2026-11 W6P1 (1130~1130)</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -832,25 +823,16 @@
         <v>10440</v>
       </c>
       <c r="BE3">
-        <v>24605</v>
+        <v>9635</v>
       </c>
       <c r="BF3">
         <v>0</v>
       </c>
       <c r="BG3">
-        <v>13274</v>
+        <v>5103</v>
       </c>
       <c r="BH3">
-        <v>13135</v>
-      </c>
-      <c r="BI3">
-        <v>6196</v>
-      </c>
-      <c r="BJ3">
-        <v>8059</v>
-      </c>
-      <c r="BK3">
-        <v>1195</v>
+        <v>4583</v>
       </c>
     </row>
     <row r="4">
@@ -1106,25 +1088,16 @@
         <v>12354</v>
       </c>
       <c r="BE5">
-        <v>27218</v>
+        <v>10657</v>
       </c>
       <c r="BF5">
         <v>0</v>
       </c>
       <c r="BG5">
-        <v>18872</v>
+        <v>7256</v>
       </c>
       <c r="BH5">
-        <v>18671</v>
-      </c>
-      <c r="BI5">
-        <v>8804</v>
-      </c>
-      <c r="BJ5">
-        <v>11458</v>
-      </c>
-      <c r="BK5">
-        <v>1700</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="6">
@@ -1927,7 +1900,7 @@
         <v>11832</v>
       </c>
       <c r="BE12">
-        <v>2784</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="13">
@@ -2021,7 +1994,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BK13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BH13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sams-demand.xlsx
+++ b/sams-demand.xlsx
@@ -734,7 +734,7 @@
         <v>10440</v>
       </c>
       <c r="BE2">
-        <v>2436</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="3">
@@ -996,7 +996,7 @@
         <v>12354</v>
       </c>
       <c r="BE4">
-        <v>5394</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="5">
@@ -1230,6 +1230,9 @@
       <c r="BD6">
         <v>4698</v>
       </c>
+      <c r="BE6">
+        <v>1566</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1451,7 +1454,7 @@
         <v>2262</v>
       </c>
       <c r="BE8">
-        <v>1218</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="9">
@@ -1674,7 +1677,7 @@
         <v>6612</v>
       </c>
       <c r="BE10">
-        <v>1914</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="11">
@@ -1900,7 +1903,7 @@
         <v>11832</v>
       </c>
       <c r="BE12">
-        <v>2958</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="13">
